--- a/config/Amazon_dropdown.xlsx
+++ b/config/Amazon_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FFC452-0302-4808-AFF4-0584538F241B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D131E-A0F6-4ABC-80D6-A83F1359B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="146">
   <si>
     <t>Attribute</t>
   </si>
@@ -475,6 +475,12 @@
   </si>
   <si>
     <t>Amazon Category</t>
+  </si>
+  <si>
+    <t>product_type#1.value</t>
+  </si>
+  <si>
+    <t>SHIRT</t>
   </si>
 </sst>
 </file>
@@ -516,226 +522,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="medium">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFFF0000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFFF0000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD4D4D4"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD4D4D4"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD4D4D4"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD4D4D4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF008000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF008000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF008000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF008000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="medium">
-          <color rgb="FFFF0000"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFFF0000"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFFF0000"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFFF0000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD4D4D4"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD4D4D4"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD4D4D4"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD4D4D4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF008000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF008000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF008000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF008000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i val="0"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1098,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FEB0F0-8794-4F72-85E1-24AFD1DB4E9B}">
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -1122,13 +909,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1136,13 +923,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1150,13 +937,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -1164,13 +951,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -1178,13 +965,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
@@ -1192,13 +979,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -1206,13 +993,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1220,13 +1007,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1234,13 +1021,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1248,13 +1035,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1262,13 +1049,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
@@ -1276,13 +1063,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1290,13 +1077,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
@@ -1304,13 +1091,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1318,13 +1105,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
@@ -1332,7 +1119,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
@@ -1346,7 +1133,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
@@ -1360,7 +1147,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
@@ -1374,7 +1161,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
@@ -1388,7 +1175,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -1402,13 +1189,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
@@ -1416,13 +1203,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1430,13 +1217,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
@@ -1444,13 +1231,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
@@ -1458,13 +1245,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
@@ -1475,7 +1262,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
@@ -1489,10 +1276,10 @@
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -1503,7 +1290,7 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
         <v>52</v>
@@ -1517,10 +1304,10 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
@@ -1531,7 +1318,7 @@
         <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
@@ -1545,10 +1332,10 @@
         <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
@@ -1559,7 +1346,7 @@
         <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
@@ -1570,13 +1357,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
@@ -1587,7 +1374,7 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
         <v>56</v>
@@ -1601,10 +1388,10 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
@@ -1615,7 +1402,7 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
         <v>57</v>
@@ -1629,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
         <v>57</v>
@@ -1643,7 +1430,7 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
         <v>57</v>
@@ -1657,10 +1444,10 @@
         <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
@@ -1671,7 +1458,7 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
@@ -1682,13 +1469,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -1699,7 +1486,7 @@
         <v>58</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
         <v>59</v>
@@ -1713,7 +1500,7 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>59</v>
@@ -1727,7 +1514,7 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
         <v>59</v>
@@ -1741,10 +1528,10 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -1755,7 +1542,7 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
         <v>60</v>
@@ -1769,7 +1556,7 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>60</v>
@@ -1783,7 +1570,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
         <v>60</v>
@@ -1794,13 +1581,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -1811,7 +1598,7 @@
         <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C51" t="s">
         <v>62</v>
@@ -1825,7 +1612,7 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
         <v>62</v>
@@ -1839,7 +1626,7 @@
         <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
         <v>62</v>
@@ -1853,7 +1640,7 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
         <v>62</v>
@@ -1867,7 +1654,7 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C55" t="s">
         <v>62</v>
@@ -1881,7 +1668,7 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
         <v>62</v>
@@ -1895,7 +1682,7 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C57" t="s">
         <v>62</v>
@@ -1906,13 +1693,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -1923,7 +1710,7 @@
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
         <v>65</v>
@@ -1937,7 +1724,7 @@
         <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="C60" t="s">
         <v>65</v>
@@ -1951,7 +1738,7 @@
         <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
         <v>65</v>
@@ -1965,10 +1752,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
@@ -1979,7 +1766,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="C63" t="s">
         <v>64</v>
@@ -1993,7 +1780,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
         <v>64</v>
@@ -2007,7 +1794,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
         <v>64</v>
@@ -2018,13 +1805,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
@@ -2035,10 +1822,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -2049,10 +1836,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
@@ -2063,10 +1850,10 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
@@ -2077,10 +1864,10 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
@@ -2091,10 +1878,10 @@
         <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
@@ -2105,7 +1892,7 @@
         <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
         <v>73</v>
@@ -2119,10 +1906,10 @@
         <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
@@ -2133,10 +1920,10 @@
         <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
@@ -2147,10 +1934,10 @@
         <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
@@ -2161,10 +1948,10 @@
         <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -2175,10 +1962,10 @@
         <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -2189,10 +1976,10 @@
         <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
@@ -2203,10 +1990,10 @@
         <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
@@ -2217,10 +2004,10 @@
         <v>66</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
@@ -2231,10 +2018,10 @@
         <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -2245,10 +2032,10 @@
         <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
@@ -2259,10 +2046,10 @@
         <v>66</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -2273,10 +2060,10 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
@@ -2287,10 +2074,10 @@
         <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
@@ -2301,10 +2088,10 @@
         <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -2315,10 +2102,10 @@
         <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
@@ -2329,10 +2116,10 @@
         <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -2343,10 +2130,10 @@
         <v>66</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
@@ -2357,10 +2144,10 @@
         <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
@@ -2371,10 +2158,10 @@
         <v>66</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
@@ -2382,13 +2169,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -2399,10 +2186,10 @@
         <v>106</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
@@ -2413,10 +2200,10 @@
         <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
@@ -2427,10 +2214,10 @@
         <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
@@ -2441,10 +2228,10 @@
         <v>106</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
@@ -2455,10 +2242,10 @@
         <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
@@ -2469,10 +2256,10 @@
         <v>106</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -2483,10 +2270,10 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -2497,10 +2284,10 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C100" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
@@ -2511,10 +2298,10 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -2525,10 +2312,10 @@
         <v>106</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -2539,10 +2326,10 @@
         <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
@@ -2553,10 +2340,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -2567,10 +2354,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
@@ -2581,10 +2368,10 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C106" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
@@ -2595,10 +2382,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D107" t="s">
         <v>5</v>
@@ -2609,10 +2396,10 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C108" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
@@ -2623,10 +2410,10 @@
         <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
@@ -2637,10 +2424,10 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C110" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
@@ -2648,13 +2435,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C111" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
@@ -2662,13 +2449,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C112" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
@@ -2676,13 +2463,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C113" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
@@ -2693,10 +2480,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
@@ -2707,10 +2494,10 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -2718,13 +2505,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
@@ -2735,10 +2522,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
@@ -2746,13 +2533,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
@@ -2763,10 +2550,10 @@
         <v>123</v>
       </c>
       <c r="B119" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
@@ -2777,7 +2564,7 @@
         <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
         <v>4</v>
@@ -2788,13 +2575,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C121" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
@@ -2802,13 +2589,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -2819,7 +2606,7 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s">
         <v>133</v>
@@ -2830,13 +2617,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C124" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -2844,13 +2631,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C125" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -2861,7 +2648,7 @@
         <v>136</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C126" t="s">
         <v>137</v>
@@ -2875,10 +2662,10 @@
         <v>136</v>
       </c>
       <c r="B127" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -2889,7 +2676,7 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C128" t="s">
         <v>139</v>
@@ -2903,10 +2690,10 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C129" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -2917,12 +2704,26 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C130" t="s">
         <v>141</v>
       </c>
       <c r="D130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131" t="s">
+        <v>141</v>
+      </c>
+      <c r="D131" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config/Amazon_dropdown.xlsx
+++ b/config/Amazon_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0D131E-A0F6-4ABC-80D6-A83F1359B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFC24A6-8618-44BB-B1D0-E7B8B02445B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="148">
   <si>
     <t>Attribute</t>
   </si>
@@ -481,6 +481,12 @@
   </si>
   <si>
     <t>SHIRT</t>
+  </si>
+  <si>
+    <t>Sky Blue</t>
+  </si>
+  <si>
+    <t>Yellow</t>
   </si>
 </sst>
 </file>
@@ -548,9 +554,9 @@
       <sheetName val="Conditions List"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3">
         <row r="2">
           <cell r="AE2" t="str">
@@ -885,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FEB0F0-8794-4F72-85E1-24AFD1DB4E9B}">
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -2508,10 +2514,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C116" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
@@ -2519,13 +2525,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="C117" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
@@ -2533,13 +2539,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
@@ -2547,13 +2553,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
@@ -2561,13 +2567,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="C120" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
@@ -2578,10 +2584,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C121" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
@@ -2589,13 +2595,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -2603,13 +2609,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C123" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
@@ -2617,13 +2623,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -2631,13 +2637,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -2645,13 +2651,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B126" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -2659,13 +2665,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -2676,10 +2682,10 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -2690,10 +2696,10 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -2704,10 +2710,10 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -2718,12 +2724,40 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
+        <v>140</v>
+      </c>
+      <c r="C131" t="s">
+        <v>139</v>
+      </c>
+      <c r="D131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132" t="s">
+        <v>141</v>
+      </c>
+      <c r="C132" t="s">
+        <v>141</v>
+      </c>
+      <c r="D132" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" t="s">
         <v>142</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C133" t="s">
         <v>141</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D133" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config/Amazon_dropdown.xlsx
+++ b/config/Amazon_dropdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\our data\KPA\NEW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFC24A6-8618-44BB-B1D0-E7B8B02445B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32AC833-099E-425C-B927-237A661860C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="748" xr2:uid="{C0D2C78A-6BFE-401C-9027-E5C9268B4C7B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="152">
   <si>
     <t>Attribute</t>
   </si>
@@ -487,6 +487,18 @@
   </si>
   <si>
     <t>Yellow</t>
+  </si>
+  <si>
+    <t>Machine Wash. Dry Inside Out, In Shade.</t>
+  </si>
+  <si>
+    <t>60% Cotton 40% Polyester</t>
+  </si>
+  <si>
+    <t>Cotton Blend</t>
+  </si>
+  <si>
+    <t>Regular Machine Wash</t>
   </si>
 </sst>
 </file>
@@ -891,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FEB0F0-8794-4F72-85E1-24AFD1DB4E9B}">
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
@@ -2469,13 +2481,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
@@ -2483,13 +2495,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="D114" t="s">
         <v>5</v>
@@ -2500,10 +2512,10 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -2514,10 +2526,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
@@ -2528,10 +2540,10 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D117" t="s">
         <v>5</v>
@@ -2542,10 +2554,10 @@
         <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="D118" t="s">
         <v>5</v>
@@ -2553,13 +2565,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
@@ -2570,10 +2582,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
@@ -2581,13 +2593,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
@@ -2598,10 +2610,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C122" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -2612,7 +2624,7 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="C123" t="s">
         <v>4</v>
@@ -2623,13 +2635,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C124" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -2637,13 +2649,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -2651,13 +2663,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C126" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -2665,13 +2677,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="C127" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -2679,13 +2691,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -2693,13 +2705,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -2707,13 +2719,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -2724,10 +2736,10 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -2738,10 +2750,10 @@
         <v>136</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -2752,12 +2764,54 @@
         <v>136</v>
       </c>
       <c r="B133" t="s">
+        <v>139</v>
+      </c>
+      <c r="C133" t="s">
+        <v>139</v>
+      </c>
+      <c r="D133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>140</v>
+      </c>
+      <c r="C134" t="s">
+        <v>139</v>
+      </c>
+      <c r="D134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" t="s">
+        <v>141</v>
+      </c>
+      <c r="C135" t="s">
+        <v>141</v>
+      </c>
+      <c r="D135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
         <v>142</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C136" t="s">
         <v>141</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D136" t="s">
         <v>5</v>
       </c>
     </row>
